--- a/tasks/HR_Troutly_T2v2_pto_liability_close/05_rubric_import.xlsx
+++ b/tasks/HR_Troutly_T2v2_pto_liability_close/05_rubric_import.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The cutover memo caps carryover at 40.0 hours, accrues four posted periods at the tier over 26 and values each balance at the rate on file over 2,080. The 52 rows sum to $92,739.54, or $92,772.88 rounding each posting.</t>
+          <t>The cutover memo caps carryover at 40.0 hours, accrues four posted periods at the tier over 26 and values each balance at the rate on file over 2,080. The 52 balances sum to $92,739.54, or $92,772.88 rounding each posting.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -681,12 +681,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
+          <t>States, on the PTO liability page, PTO hours of 297.79 for Customer Success.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hosana carries 117.12 hours on the HRIS report and the archive holds 92.50 at 06/30/2026. The cutover memo caps carryover at 40.0 hours, and four periods at the 160-hour tier add 24.6152.</t>
+          <t>In Customer Success the cutover memo caps TRT-0021 at 40.0 hours, the archive puts TRT-0083 at the 120-hour tier, handbook 2.2 prorates TRT-0141 and TRT-0153 accrues from the start. The line holds 297.79 hours, the HRIS report 322.95.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 64.62 hours for Krystale Jumawan, TRT-0009.</t>
+          <t>States, on the PTO liability page, a PTO liability of $12,627.20 for Customer Success.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Jumawan carries 108.62 hours on the HRIS report and the archive holds 84.00 at 06/30/2026. The cutover memo caps carryover at 40.0 hours, and four periods at the 160-hour tier add 24.6152.</t>
+          <t>Handbook 3.2 and 5.4 put TRT-0088 at $118,000.00 and TRT-0096 at $61,000.00, and the roster puts TRT-0153 at $92,000.00. On those rates and the capped balances Customer Success carries $12,627.20 against the load's $14,023.72.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K6" s="2" t="n"/>
@@ -791,12 +791,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 18.46 hours for Jessica Ko, TRT-0012.</t>
+          <t>States, on the PTO liability page, PTO hours of 558.31 for Engineering.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ko carries 49.96 hours on the HRIS report and the archive holds 71.50 at 06/30/2026. The cutover memo caps carryover at 40.0 hours, and four periods at the 120-hour tier add 18.4616.</t>
+          <t>Five Engineering balances sit over the cutover memo's 40.0-hour cap, TRT-0005 at 92.50 in the archive, and the archive puts TRT-0051 at the 120-hour tier. Engineering holds 558.31 hours against the HRIS report's 694.66.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K7" s="2" t="n"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
+          <t>States, on the PTO liability page, a PTO liability of $41,542.16 for Engineering.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>The archive dates Thornbury's service from 08/09/2021 and her capped opening is 40.00 hours. She reaches five years on 08/09/2026 inside the fourth posted period, so the cutover memo accrues three periods of 4.6154 hours and one of 6.1538.</t>
+          <t>The signed amendment sets TRT-0117 at $148,200.00 from 05/16/2026 over the loaded $138,000.00. With the capped balances Engineering carries $41,542.16 of liability against the load's $52,936.56.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 42.46 hours for Edith Bustamante, TRT-0021.</t>
+          <t>States, on the PTO liability page, PTO hours of 121.53 for Finance and Corporate.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Bustamante carries 76.46 hours on the HRIS report and the archive holds 58.50 at 06/30/2026. The cutover memo caps carryover at 40.0 hours, and four periods at the 120-hour tier add 18.4616.</t>
+          <t>Finance and Corporate has one balance over the cap, TRT-0009 at 84.00 in the archive, which the cutover memo holds to 40.0 hours. The line holds 121.53 hours against the HRIS report's 165.53.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -956,12 +956,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 58.46 hours for Rohan Iyer, TRT-0014.</t>
+          <t>States, on the PTO liability page, a PTO liability of $8,187.68 for Finance and Corporate.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Iyer carries 84.46 hours on the HRIS report and the archive holds 66.00 at 06/30/2026. The cutover memo caps carryover at 40.0 hours, and four periods at the 120-hour tier add 18.4616.</t>
+          <t>Capping TRT-0009 under the cutover memo takes Finance and Corporate to $8,187.68 at the rates on the roster. The load values the same five employees at $11,121.71.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 58.46 hours for Maeve Oyinlola, TRT-0023.</t>
+          <t>States, on the PTO liability page, PTO hours of 170.50 for Product.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Oyinlola carries 78.96 hours on the HRIS report and the archive holds 60.50 at 06/30/2026. The cutover memo caps carryover at 40.0 hours, and four periods at the 120-hour tier add 18.4616.</t>
+          <t>Product nets close to the load because the cutover memo caps TRT-0040 while handbook 7.6 bridges TRT-0071 and the archive puts TRT-0079 at the 120-hour tier. It holds 170.50 hours against the HRIS report's 161.54.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 26.46 hours for Zephyr Adebayo, TRT-0031.</t>
+          <t>States, on the PTO liability page, a PTO liability of $10,984.34 for Product.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Adebayo carries 38.46 hours on the HRIS report and the archive holds 52.00 at 06/30/2026. The cutover memo caps carryover at 40.0 hours, and four periods at the 120-hour tier add 18.4616.</t>
+          <t>At the rates on the roster the Product line carries $10,984.34, the cap on TRT-0040 offset by the bridged TRT-0071 and the retiered TRT-0079 under the cutover memo. The load carries $10,957.00.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K12" s="2" t="n"/>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 50.46 hours for Emeka Thorsen, TRT-0029.</t>
+          <t>States, on the PTO liability page, PTO hours of 374.04 for Sales and Marketing.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Thorsen carries 67.46 hours on the HRIS report and the archive holds 57.00 at 06/30/2026. The cutover memo caps carryover at 40.0 hours, and four periods at the 120-hour tier add 18.4616.</t>
+          <t>The request joins Sales and Marketing. The cutover memo caps TRT-0018, TRT-0029 and TRT-0043, times TRT-0018's tier change and accrues TRT-0155 from the start, 374.04 hours against the HRIS report's 407.03.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K13" s="2" t="n"/>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 58.46 hours for Ilse Van der Kolk, TRT-0040.</t>
+          <t>States, on the PTO liability page, a PTO liability of $19,398.16 for Sales and Marketing.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Kolk carries 67.96 hours on the HRIS report and the archive holds 49.50 at 06/30/2026. The cutover memo caps carryover at 40.0 hours, and four periods at the 120-hour tier add 18.4616.</t>
+          <t>Valued at the roster's rates, TRT-0155 at $56,300.00, the joined Sales and Marketing line carries $19,398.16 under the cutover memo. The load's figures for the same 13 employees come to $22,061.40.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1209,782 +1209,12 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, a balance of 51.87 hours for Samuel Burkenham, TRT-0071.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Burkenham's archive service bridges a 241-day break under the handbook's 7.6, five completed years at 08/31/2026. Four posted periods accrue at the 160-hour tier, so 51.87 hours stand against the HRIS report's 39.56.</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, a balance of 6.71 hours for Priyamvada Raghunath, TRT-0051.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Raghunath reads the 80-hour tier in BambooHR and the archive dates the hire 05/03/2022, four completed years at 08/31/2026. The cutover memo accrues at the 120-hour tier, so 6.71 hours stand against the HRIS report's 0.56.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, a balance of 24.96 hours for Wren Takahashi-Bell, TRT-0079.</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Takahashi-Bell reads the 80-hour tier in BambooHR and the archive dates the hire 02/06/2023, three completed years at 08/31/2026. The cutover memo accrues at the 120-hour tier, so 24.96 hours stand against the HRIS report's 18.81.</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, a balance of 40.96 hours for Callum Oyelaran, TRT-0058.</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Oyelaran reads the 80-hour tier in BambooHR and the archive dates the hire 09/12/2022, three completed years at 08/31/2026. The cutover memo accrues at the 120-hour tier, so 40.96 hours stand against the HRIS report's 34.81.</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, a balance of 18.71 hours for Desmond Achterberg, TRT-0083.</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Achterberg reads the 80-hour tier in BambooHR and the archive dates the hire 06/19/2023, three completed years at 08/31/2026. The cutover memo accrues at the 120-hour tier, so 18.71 hours stand against the HRIS report's 12.56.</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Okonkwo started 07/22/2026 on the roster and the crosswalk marks TRT-0153 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours a period since the start.</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, an hourly rate of $44.2308 for Simone Okonkwo, TRT-0153.</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Okonkwo's roster salary of $92,000.00 over 2,080 is $44.2308 an hour, and the crosswalk marks TRT-0153 Never Loaded with no BambooHR rate against it.</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, a balance of 34.46 hours for Oren Kastellanos, TRT-0043.</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Kastellanos carries 31.81 hours on the HRIS report and the archive holds 43.50 at 06/30/2026. The cutover memo caps carryover at 40.0 hours, and four periods at the 120-hour tier add 18.4616.</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>The signed promotion approval sets Featherstone's salary at $118,000.00 from 06/16/2026 and the handbook's 3.2 puts the signed document over the record. BambooHR carries $104,000.00. $118,000.00 over 2,080 is $56.7308.</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Ibarra started 08/03/2026 on the roster and the crosswalk marks TRT-0155 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours a period since the start.</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, an hourly rate of $27.0673 for Rafael Ibarra, TRT-0155.</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Ibarra's roster salary of $56,300.00 over 2,080 is $27.0673 an hour, and the crosswalk marks TRT-0155 Never Loaded with no BambooHR rate against it.</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>The schedule change form moves Quintanilla from 25 to 32 hours a week on 08/10/2026 and the handbook's 2.2 accrues part-time hours pro-rata under 30. The HRIS report accrues her at a full week and shows 33.06 hours.</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>The signed amendment sets Luk's salary at $148,200.00 from 05/16/2026 and the archive recorded it. BambooHR carries the loaded $138,000.00, and $148,200.00 over 2,080 is $71.2500.</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>App DB Programatic</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Marchetti's offer letter carries the Support Specialist step on each anniversary and the handbook's 5.4 sets it at $3,000.00. Her anniversary fell 08/17/2026, so the rate on file is $61,000.00, $29.3269 an hour.</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Final Response</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Expert Assessment</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/tasks/HR_Troutly_T2v2_pto_liability_close/05_rubric_import.xlsx
+++ b/tasks/HR_Troutly_T2v2_pto_liability_close/05_rubric_import.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_31202a8918284a76a7c53582bfc550ec", "transformations": []}]</t>
         </is>
       </c>
       <c r="K2" s="2" t="n"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_31202a8918284a76a7c53582bfc550ec", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -769,7 +769,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_31202a8918284a76a7c53582bfc550ec", "transformations": []}, {"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K6" s="2" t="n"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_31202a8918284a76a7c53582bfc550ec", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K7" s="2" t="n"/>
@@ -879,7 +879,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_31202a8918284a76a7c53582bfc550ec", "transformations": []}, {"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_31202a8918284a76a7c53582bfc550ec", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_31202a8918284a76a7c53582bfc550ec", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_31202a8918284a76a7c53582bfc550ec", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_31202a8918284a76a7c53582bfc550ec", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K12" s="2" t="n"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_31202a8918284a76a7c53582bfc550ec", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K13" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_1e12795ed0df4d489a36382afdb63279", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_31202a8918284a76a7c53582bfc550ec", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
